--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7837bf4cf90b2e58/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{0DA6D88D-0774-4C28-87E0-FD38E60E30B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2E64F17-4CC0-480D-B5D1-6E77BF8C5A30}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{0DA6D88D-0774-4C28-87E0-FD38E60E30B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD45BD76-A623-43CE-9CFB-F99E7D4B7C6F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CB4930A4-50B8-4A4E-B8F6-80E9921E8E4F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>nama</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>nama5</t>
+  </si>
+  <si>
+    <t>&lt;&lt; jangan diganti</t>
   </si>
 </sst>
 </file>
@@ -444,6 +447,9 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="19.5" x14ac:dyDescent="0.3">
